--- a/results/summary_table.xlsx
+++ b/results/summary_table.xlsx
@@ -617,16 +617,16 @@
         <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1710765000007086</v>
+        <v>0.08433040000090841</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1409016999996311</v>
+        <v>0.09669389999908162</v>
       </c>
       <c r="M4" t="n">
-        <v>7.647178300000633</v>
+        <v>3.622965099999419</v>
       </c>
       <c r="N4" t="n">
-        <v>2.438313700000435</v>
+        <v>1.758664600001794</v>
       </c>
     </row>
     <row r="5">
@@ -659,16 +659,16 @@
         <v>247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1445136000002094</v>
+        <v>0.05593130000124802</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1128467999997156</v>
+        <v>0.05153760000030161</v>
       </c>
       <c r="M5" t="n">
-        <v>4.769082400000116</v>
+        <v>1.870501299999887</v>
       </c>
       <c r="N5" t="n">
-        <v>2.216449600000487</v>
+        <v>1.165423099999316</v>
       </c>
     </row>
     <row r="6">
@@ -701,16 +701,16 @@
         <v>181</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1079528000000209</v>
+        <v>0.03071329999875161</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07097370000064984</v>
+        <v>0.03681219999998575</v>
       </c>
       <c r="M6" t="n">
-        <v>1.765021299999717</v>
+        <v>0.7821442999993451</v>
       </c>
       <c r="N6" t="n">
-        <v>1.366011799999796</v>
+        <v>0.8775707999993756</v>
       </c>
     </row>
     <row r="7">
@@ -743,16 +743,16 @@
         <v>115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02363409999998112</v>
+        <v>0.01128959999914514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03791689999980008</v>
+        <v>0.01928319999933592</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09380669999973179</v>
+        <v>0.03217589999985648</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8983594000001176</v>
+        <v>0.5265241999986756</v>
       </c>
     </row>
     <row r="8">
@@ -789,16 +789,16 @@
         <v>99</v>
       </c>
       <c r="K8" t="n">
-        <v>1.689453500000127</v>
+        <v>0.9726895000021614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2993876000000455</v>
+        <v>0.3076309999996738</v>
       </c>
       <c r="M8" t="n">
-        <v>62.75721389999944</v>
+        <v>31.41149170000062</v>
       </c>
       <c r="N8" t="n">
-        <v>6.687324499999704</v>
+        <v>4.80463840000084</v>
       </c>
     </row>
     <row r="9">
@@ -831,16 +831,16 @@
         <v>78</v>
       </c>
       <c r="K9" t="n">
-        <v>1.811751500000355</v>
+        <v>0.7991468000000168</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2324294999998529</v>
+        <v>0.2385383000000729</v>
       </c>
       <c r="M9" t="n">
-        <v>38.77415930000006</v>
+        <v>19.33992669999861</v>
       </c>
       <c r="N9" t="n">
-        <v>5.243911900000057</v>
+        <v>3.832183499998791</v>
       </c>
     </row>
     <row r="10">
@@ -873,16 +873,16 @@
         <v>57</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8955988999996407</v>
+        <v>0.5075418999986141</v>
       </c>
       <c r="L10" t="n">
-        <v>0.160427200000413</v>
+        <v>0.1643644000032509</v>
       </c>
       <c r="M10" t="n">
-        <v>15.49612439999964</v>
+        <v>7.403228099999978</v>
       </c>
       <c r="N10" t="n">
-        <v>3.992202600000383</v>
+        <v>2.74356820000321</v>
       </c>
     </row>
     <row r="11">
@@ -915,16 +915,16 @@
         <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3034475999993447</v>
+        <v>0.1825482000022021</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1037894000000961</v>
+        <v>0.09199470000021392</v>
       </c>
       <c r="M11" t="n">
-        <v>1.184615199999826</v>
+        <v>0.6662394000013592</v>
       </c>
       <c r="N11" t="n">
-        <v>2.471290899999985</v>
+        <v>1.773163699999714</v>
       </c>
     </row>
     <row r="12">
@@ -961,16 +961,16 @@
         <v>4671</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1175971000002392</v>
+        <v>0.03533400000014808</v>
       </c>
       <c r="L12" t="n">
-        <v>19.17345579999983</v>
+        <v>10.50097770000139</v>
       </c>
       <c r="M12" t="n">
-        <v>6.170415600000524</v>
+        <v>1.486297100000229</v>
       </c>
       <c r="N12" t="n">
-        <v>100.2428377000006</v>
+        <v>76.96998689999964</v>
       </c>
     </row>
     <row r="13">
@@ -1003,16 +1003,16 @@
         <v>3552</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1108796999997139</v>
+        <v>0.0397486999972898</v>
       </c>
       <c r="L13" t="n">
-        <v>14.7313022999997</v>
+        <v>11.75299710000036</v>
       </c>
       <c r="M13" t="n">
-        <v>4.731017400000383</v>
+        <v>1.735977200001798</v>
       </c>
       <c r="N13" t="n">
-        <v>77.73989590000019</v>
+        <v>59.62504040000204</v>
       </c>
     </row>
     <row r="14">
@@ -1045,16 +1045,16 @@
         <v>2433</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09903960000065126</v>
+        <v>0.02119970000057947</v>
       </c>
       <c r="L14" t="n">
-        <v>10.75422400000025</v>
+        <v>6.956799100000353</v>
       </c>
       <c r="M14" t="n">
-        <v>3.469268499999998</v>
+        <v>1.025593599999411</v>
       </c>
       <c r="N14" t="n">
-        <v>51.44029140000021</v>
+        <v>36.26640920000136</v>
       </c>
     </row>
     <row r="15">
@@ -1087,16 +1087,16 @@
         <v>1314</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08143239999935759</v>
+        <v>0.01949299999978393</v>
       </c>
       <c r="L15" t="n">
-        <v>5.435533099999702</v>
+        <v>3.72802529999899</v>
       </c>
       <c r="M15" t="n">
-        <v>1.790136100000382</v>
+        <v>0.4965947999990021</v>
       </c>
       <c r="N15" t="n">
-        <v>27.17454050000015</v>
+        <v>19.61297019999984</v>
       </c>
     </row>
     <row r="16">
@@ -1133,16 +1133,16 @@
         <v>7174</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4486187000002246</v>
+        <v>0.1838165999979537</v>
       </c>
       <c r="L16" t="n">
-        <v>56.79556529999991</v>
+        <v>28.99850700000025</v>
       </c>
       <c r="M16" t="n">
-        <v>26.3757499000003</v>
+        <v>11.48162769999908</v>
       </c>
       <c r="N16" t="n">
-        <v>386.4390162</v>
+        <v>224.2007552000032</v>
       </c>
     </row>
     <row r="17">
@@ -1175,16 +1175,16 @@
         <v>5425</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3975447999991957</v>
+        <v>0.2094176000027801</v>
       </c>
       <c r="L17" t="n">
-        <v>42.0966726000006</v>
+        <v>21.81571139999869</v>
       </c>
       <c r="M17" t="n">
-        <v>21.99656440000035</v>
+        <v>9.096856199998001</v>
       </c>
       <c r="N17" t="n">
-        <v>294.8649671000003</v>
+        <v>175.3562974999986</v>
       </c>
     </row>
     <row r="18">
@@ -1217,16 +1217,16 @@
         <v>3676</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3813907000003383</v>
+        <v>0.1677825000006123</v>
       </c>
       <c r="L18" t="n">
-        <v>29.69186530000025</v>
+        <v>31.30302099999972</v>
       </c>
       <c r="M18" t="n">
-        <v>14.9082212000003</v>
+        <v>6.681042399999569</v>
       </c>
       <c r="N18" t="n">
-        <v>194.0988326000006</v>
+        <v>130.5803974000009</v>
       </c>
     </row>
     <row r="19">
@@ -1259,16 +1259,16 @@
         <v>1927</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2676563999993959</v>
+        <v>0.1320744000004197</v>
       </c>
       <c r="L19" t="n">
-        <v>14.50376460000007</v>
+        <v>8.653061899996828</v>
       </c>
       <c r="M19" t="n">
-        <v>7.502474399999301</v>
+        <v>3.69882239999788</v>
       </c>
       <c r="N19" t="n">
-        <v>96.87882140000056</v>
+        <v>69.62509730000238</v>
       </c>
     </row>
   </sheetData>

--- a/results/summary_table.xlsx
+++ b/results/summary_table.xlsx
@@ -617,16 +617,16 @@
         <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08433040000090841</v>
+        <v>0.09226320000016131</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09669389999908162</v>
+        <v>0.1444589000002452</v>
       </c>
       <c r="M4" t="n">
-        <v>3.622965099999419</v>
+        <v>4.604598300000362</v>
       </c>
       <c r="N4" t="n">
-        <v>1.758664600001794</v>
+        <v>1.916361400000824</v>
       </c>
     </row>
     <row r="5">
@@ -659,16 +659,16 @@
         <v>247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05593130000124802</v>
+        <v>0.05989430000045104</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05153760000030161</v>
+        <v>0.06056340000031923</v>
       </c>
       <c r="M5" t="n">
-        <v>1.870501299999887</v>
+        <v>2.901971900000717</v>
       </c>
       <c r="N5" t="n">
-        <v>1.165423099999316</v>
+        <v>1.68474310000056</v>
       </c>
     </row>
     <row r="6">
@@ -701,16 +701,16 @@
         <v>181</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03071329999875161</v>
+        <v>0.06789009999920381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03681219999998575</v>
+        <v>0.03989290000026813</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7821442999993451</v>
+        <v>1.423926999999821</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8775707999993756</v>
+        <v>0.9879221999999572</v>
       </c>
     </row>
     <row r="7">
@@ -743,16 +743,16 @@
         <v>115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01128959999914514</v>
+        <v>0.01750209999954677</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01928319999933592</v>
+        <v>0.02647439999964263</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03217589999985648</v>
+        <v>0.03942429999915475</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5265241999986756</v>
+        <v>0.6681710000011662</v>
       </c>
     </row>
     <row r="8">
@@ -789,16 +789,16 @@
         <v>99</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9726895000021614</v>
+        <v>1.148875000000771</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3076309999996738</v>
+        <v>0.333852100000513</v>
       </c>
       <c r="M8" t="n">
-        <v>31.41149170000062</v>
+        <v>36.15682819999893</v>
       </c>
       <c r="N8" t="n">
-        <v>4.80463840000084</v>
+        <v>5.411553800000547</v>
       </c>
     </row>
     <row r="9">
@@ -831,16 +831,16 @@
         <v>78</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7991468000000168</v>
+        <v>0.8088499000004958</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2385383000000729</v>
+        <v>0.3193031999999221</v>
       </c>
       <c r="M9" t="n">
-        <v>19.33992669999861</v>
+        <v>21.34596299999976</v>
       </c>
       <c r="N9" t="n">
-        <v>3.832183499998791</v>
+        <v>4.368895800000246</v>
       </c>
     </row>
     <row r="10">
@@ -873,16 +873,16 @@
         <v>57</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5075418999986141</v>
+        <v>0.5465192999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1643644000032509</v>
+        <v>0.1773796000015864</v>
       </c>
       <c r="M10" t="n">
-        <v>7.403228099999978</v>
+        <v>7.994186199999604</v>
       </c>
       <c r="N10" t="n">
-        <v>2.74356820000321</v>
+        <v>3.05886019999889</v>
       </c>
     </row>
     <row r="11">
@@ -915,16 +915,16 @@
         <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1825482000022021</v>
+        <v>0.1983187999994698</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09199470000021392</v>
+        <v>0.1021783000014693</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6662394000013592</v>
+        <v>0.7030422999996517</v>
       </c>
       <c r="N11" t="n">
-        <v>1.773163699999714</v>
+        <v>2.035874499999409</v>
       </c>
     </row>
     <row r="12">
@@ -961,16 +961,16 @@
         <v>4671</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03533400000014808</v>
+        <v>0.04878690000077768</v>
       </c>
       <c r="L12" t="n">
-        <v>10.50097770000139</v>
+        <v>13.40626690000136</v>
       </c>
       <c r="M12" t="n">
-        <v>1.486297100000229</v>
+        <v>2.153369300000122</v>
       </c>
       <c r="N12" t="n">
-        <v>76.96998689999964</v>
+        <v>78.42550999999912</v>
       </c>
     </row>
     <row r="13">
@@ -1003,16 +1003,16 @@
         <v>3552</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0397486999972898</v>
+        <v>0.03152450000015961</v>
       </c>
       <c r="L13" t="n">
-        <v>11.75299710000036</v>
+        <v>12.1757362999997</v>
       </c>
       <c r="M13" t="n">
-        <v>1.735977200001798</v>
+        <v>1.479759200001354</v>
       </c>
       <c r="N13" t="n">
-        <v>59.62504040000204</v>
+        <v>61.06195549999939</v>
       </c>
     </row>
     <row r="14">
@@ -1045,16 +1045,16 @@
         <v>2433</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02119970000057947</v>
+        <v>0.03992409999955271</v>
       </c>
       <c r="L14" t="n">
-        <v>6.956799100000353</v>
+        <v>11.71900230000028</v>
       </c>
       <c r="M14" t="n">
-        <v>1.025593599999411</v>
+        <v>1.545260099999723</v>
       </c>
       <c r="N14" t="n">
-        <v>36.26640920000136</v>
+        <v>44.20116360000065</v>
       </c>
     </row>
     <row r="15">
@@ -1087,16 +1087,16 @@
         <v>1314</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01949299999978393</v>
+        <v>0.02330839999922318</v>
       </c>
       <c r="L15" t="n">
-        <v>3.72802529999899</v>
+        <v>3.693872699999702</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4965947999990021</v>
+        <v>0.5207531000014569</v>
       </c>
       <c r="N15" t="n">
-        <v>19.61297019999984</v>
+        <v>22.2550183000003</v>
       </c>
     </row>
     <row r="16">
@@ -1133,16 +1133,16 @@
         <v>7174</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1838165999979537</v>
+        <v>0.2642046999972081</v>
       </c>
       <c r="L16" t="n">
-        <v>28.99850700000025</v>
+        <v>62.32910199999969</v>
       </c>
       <c r="M16" t="n">
-        <v>11.48162769999908</v>
+        <v>13.84018469999864</v>
       </c>
       <c r="N16" t="n">
-        <v>224.2007552000032</v>
+        <v>295.6419326999967</v>
       </c>
     </row>
     <row r="17">
@@ -1175,16 +1175,16 @@
         <v>5425</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2094176000027801</v>
+        <v>0.1990863000028185</v>
       </c>
       <c r="L17" t="n">
-        <v>21.81571139999869</v>
+        <v>40.90166409999802</v>
       </c>
       <c r="M17" t="n">
-        <v>9.096856199998001</v>
+        <v>11.07074549999743</v>
       </c>
       <c r="N17" t="n">
-        <v>175.3562974999986</v>
+        <v>211.6369372000008</v>
       </c>
     </row>
     <row r="18">
@@ -1217,16 +1217,16 @@
         <v>3676</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1677825000006123</v>
+        <v>0.1864691999999195</v>
       </c>
       <c r="L18" t="n">
-        <v>31.30302099999972</v>
+        <v>34.48241269999926</v>
       </c>
       <c r="M18" t="n">
-        <v>6.681042399999569</v>
+        <v>7.396072800000184</v>
       </c>
       <c r="N18" t="n">
-        <v>130.5803974000009</v>
+        <v>153.2921692</v>
       </c>
     </row>
     <row r="19">
@@ -1259,16 +1259,16 @@
         <v>1927</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1320744000004197</v>
+        <v>0.1493538999984594</v>
       </c>
       <c r="L19" t="n">
-        <v>8.653061899996828</v>
+        <v>17.5719136000007</v>
       </c>
       <c r="M19" t="n">
-        <v>3.69882239999788</v>
+        <v>4.042688999999882</v>
       </c>
       <c r="N19" t="n">
-        <v>69.62509730000238</v>
+        <v>84.84626200000093</v>
       </c>
     </row>
   </sheetData>
